--- a/data/chapter2/FREDv3subset/state_conflicts.xlsx
+++ b/data/chapter2/FREDv3subset/state_conflicts.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="305" documentId="11_F25DC773A252ABDACC1048FDB99E5A8E5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5C05750-F410-4D58-BB99-0B5249CBFA2A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="state_conflicts" sheetId="4" r:id="rId1"/>
@@ -580,8 +580,8 @@
   <autoFilter ref="A1:C68" xr:uid="{94A66970-29A1-4ABD-AEBE-D0A24611F563}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7D5055AE-5791-4C1F-A5D9-BD7F62E12A31}" name="binominal" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{CCCF8186-328A-492F-AF4E-343C0E157695}" name="actual_publication_reports_in_fungalroot" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{E697EBF1-06BD-4B49-AF8F-6BB250377B9E}" name="fungalroot_agreed_species_state" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{CCCF8186-328A-492F-AF4E-343C0E157695}" name="actual_publication_reports_in_fungalroot" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{E697EBF1-06BD-4B49-AF8F-6BB250377B9E}" name="fungalroot_agreed_species_state" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/data/chapter2/FREDv3subset/state_conflicts.xlsx
+++ b/data/chapter2/FREDv3subset/state_conflicts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FREDv3subset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_F25DC773A252ABDACC1048FDB99E5A8E5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF06B22-E06E-4F25-9461-0B9041C2FF25}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="11_F25DC773A252ABDACC1048FDB99E5A8E5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7AF097C-ADE4-44D6-BC0E-CF283F1DD1C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="114">
   <si>
     <t>binominal</t>
   </si>
@@ -263,6 +263,9 @@
     <t>AM/EcM/NM</t>
   </si>
   <si>
+    <t>EcM/NM</t>
+  </si>
+  <si>
     <t>fungalroot_agreed_species_state</t>
   </si>
   <si>
@@ -366,6 +369,15 @@
   </si>
   <si>
     <t>Sorbus discolor</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>genus_generalized</t>
+  </si>
+  <si>
+    <t>Euptelea pleiosperma</t>
   </si>
 </sst>
 </file>
@@ -401,14 +413,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -436,15 +454,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{94A66970-29A1-4ABD-AEBE-D0A24611F563}" name="all_state_conflicts_1" displayName="all_state_conflicts_1" ref="A1:C101" totalsRowShown="0">
-  <autoFilter ref="A1:C101" xr:uid="{94A66970-29A1-4ABD-AEBE-D0A24611F563}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C81">
-    <sortCondition ref="A1:A81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{94A66970-29A1-4ABD-AEBE-D0A24611F563}" name="all_state_conflicts_1" displayName="all_state_conflicts_1" ref="A1:D102" totalsRowShown="0">
+  <autoFilter ref="A1:D102" xr:uid="{94A66970-29A1-4ABD-AEBE-D0A24611F563}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D102">
+    <sortCondition ref="A1:A102"/>
   </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7D5055AE-5791-4C1F-A5D9-BD7F62E12A31}" name="binominal" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{CCCF8186-328A-492F-AF4E-343C0E157695}" name="actual_publication_reports_in_fungalroot" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{E697EBF1-06BD-4B49-AF8F-6BB250377B9E}" name="fungalroot_agreed_species_state" dataDxfId="0"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7D5055AE-5791-4C1F-A5D9-BD7F62E12A31}" name="binominal" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{CCCF8186-328A-492F-AF4E-343C0E157695}" name="actual_publication_reports_in_fungalroot" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{E697EBF1-06BD-4B49-AF8F-6BB250377B9E}" name="fungalroot_agreed_species_state" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{64B58A0A-0160-499D-B58D-BA8733699E11}" name="genus_generalized" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -713,28 +732,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93910FF3-214F-4CDE-B36B-361ACB666C10}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.28515625" customWidth="1"/>
     <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -742,8 +765,9 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -753,8 +777,9 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,8 +789,9 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -775,8 +801,9 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -786,8 +813,9 @@
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -797,32 +825,35 @@
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>74</v>
@@ -830,915 +861,1107 @@
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B62" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B80" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="1"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B83" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B84" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B86" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B88" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="1"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="1"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="1"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="1"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="1"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B97" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="1"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B100" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="D101" s="1"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
+      <c r="B102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
